--- a/experiment/SRForm2_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/SRForm2_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.16</v>
+        <v>27.28</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7558</v>
+        <v>0.7588</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.17</v>
+        <v>26.31</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7962</v>
+        <v>0.8018999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.57</v>
+        <v>23.71</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6671</v>
+        <v>0.6771</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.75</v>
+        <v>22.63</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8133</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.99</v>
+        <v>26.97</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9374</v>
+        <v>0.9379</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.16</v>
+        <v>22.2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6105</v>
+        <v>0.6132</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.2</v>
+        <v>29.27</v>
       </c>
       <c r="C8" t="n">
-        <v>0.854</v>
+        <v>0.8557</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.17</v>
+        <v>21.22</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6348</v>
+        <v>0.6415</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.41</v>
+        <v>33.65</v>
       </c>
       <c r="C10" t="n">
-        <v>0.919</v>
+        <v>0.9234</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26.52</v>
+        <v>26.76</v>
       </c>
       <c r="C11" t="n">
-        <v>0.873</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.89</v>
+        <v>17.88</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7832</v>
+        <v>0.7826</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.61</v>
+        <v>23.67</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7131</v>
+        <v>0.7185</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.08</v>
+        <v>29.27</v>
       </c>
       <c r="C14" t="n">
-        <v>0.824</v>
+        <v>0.8304</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.22</v>
+        <v>22.26</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6734</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.61</v>
+        <v>25.78</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7199</v>
+        <v>0.7257</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.45</v>
+        <v>29.5</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9054</v>
+        <v>0.9066</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.27</v>
+        <v>25.35</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8101</v>
+        <v>0.8147</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.28</v>
+        <v>26.29</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7087</v>
+        <v>0.7105</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.25</v>
+        <v>21.45</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7881</v>
+        <v>0.7947</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.83</v>
+        <v>21.87</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7033</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.54</v>
+        <v>29.52</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7815</v>
+        <v>0.7808</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25.91</v>
+        <v>25.99</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7497</v>
+        <v>0.7553</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29.95</v>
+        <v>30.12</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9073</v>
+        <v>0.9115</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.68</v>
+        <v>19.77</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6246</v>
+        <v>0.6284</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>30.98</v>
+        <v>31.48</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8883</v>
+        <v>0.8923</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.43</v>
+        <v>27.59</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6828</v>
+        <v>0.6891</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.02</v>
+        <v>28.1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7873</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.07</v>
+        <v>31.15</v>
       </c>
       <c r="C29" t="n">
-        <v>0.871</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26.47</v>
+        <v>26.55</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.06</v>
+        <v>24.22</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7857</v>
+        <v>0.7925</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23.9</v>
+        <v>24.01</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7736</v>
+        <v>0.7806</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.55</v>
+        <v>28.82</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8384</v>
+        <v>0.8457</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26.75</v>
+        <v>26.87</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.82</v>
+        <v>22.89</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5746</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.22</v>
+        <v>28.47</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8556</v>
+        <v>0.8612</v>
       </c>
     </row>
     <row r="37">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.55</v>
+        <v>28.52</v>
       </c>
       <c r="C37" t="n">
         <v>0.8806</v>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.18</v>
+        <v>26.19</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7912</v>
+        <v>0.7952</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26.7</v>
+        <v>26.85</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6704</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22.62</v>
+        <v>22.74</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7205</v>
+        <v>0.7271</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         <v>26.8</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9342</v>
+        <v>0.9331</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25.28</v>
+        <v>25.5</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8593</v>
+        <v>0.8647</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.47</v>
+        <v>28.36</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8781</v>
+        <v>0.8778</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30.4</v>
+        <v>30.85</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9254</v>
+        <v>0.9276</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30.89</v>
+        <v>30.91</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8519</v>
+        <v>0.8531</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.41</v>
+        <v>24.27</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7117</v>
+        <v>0.7149</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.42</v>
+        <v>23.46</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.7478</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.61</v>
+        <v>21.72</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7514</v>
+        <v>0.7605</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.9</v>
+        <v>20.09</v>
       </c>
       <c r="C49" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.8033</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.06</v>
+        <v>23.18</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7318</v>
+        <v>0.7376</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.07</v>
+        <v>25.13</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7569</v>
+        <v>0.7631</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26.96</v>
+        <v>27.12</v>
       </c>
       <c r="C52" t="n">
-        <v>0.833</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>27.9</v>
+        <v>27.99</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8867</v>
+        <v>0.8893</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>21.96</v>
+        <v>22.08</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7094</v>
+        <v>0.7155</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>20.94</v>
+        <v>21</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6323</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.68</v>
+        <v>31.56</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9373</v>
+        <v>0.9376</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24.53</v>
+        <v>24.66</v>
       </c>
       <c r="C57" t="n">
-        <v>0.762</v>
+        <v>0.7687</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30.12</v>
+        <v>30.37</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8801</v>
+        <v>0.8853</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.22</v>
+        <v>25.43</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8415</v>
+        <v>0.8478</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>21.63</v>
+        <v>21.72</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7421</v>
+        <v>0.7468</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.36</v>
+        <v>22.42</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5502</v>
+        <v>0.5553</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.37</v>
+        <v>24.35</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7372</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.08</v>
+        <v>21.26</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7748</v>
+        <v>0.7847</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.1</v>
+        <v>22.14</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.6116</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.35</v>
+        <v>26.37</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7758</v>
+        <v>0.7768</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.18</v>
+        <v>25.22</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7077</v>
+        <v>0.7121</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.15</v>
+        <v>22.17</v>
       </c>
       <c r="C67" t="n">
-        <v>0.638</v>
+        <v>0.6405</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19.33</v>
+        <v>19.5</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8609</v>
+        <v>0.8636</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>29.84</v>
+        <v>29.95</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8747</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.49</v>
+        <v>24.56</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7446</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.05</v>
+        <v>22.09</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5887</v>
+        <v>0.5915</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27.58</v>
+        <v>27.79</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6474</v>
+        <v>0.6558</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>19.65</v>
+        <v>19.7</v>
       </c>
       <c r="C73" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.8008999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>19.88</v>
+        <v>20.28</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5351</v>
+        <v>0.5547</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.24</v>
+        <v>23.41</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6718</v>
+        <v>0.6859</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>30.9</v>
+        <v>31.12</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8761</v>
+        <v>0.8784999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.58</v>
+        <v>22.63</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6642</v>
+        <v>0.6681</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>26.98</v>
+        <v>27.02</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7589</v>
+        <v>0.7616000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.1</v>
+        <v>25.17</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6819</v>
+        <v>0.6862</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.17</v>
+        <v>35.33</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9500999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.91</v>
+        <v>36.21</v>
       </c>
       <c r="C82" t="n">
         <v>0.9655</v>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>31.92</v>
+        <v>32.21</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9354</v>
+        <v>0.9367</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>21.97</v>
+        <v>22.03</v>
       </c>
       <c r="C84" t="n">
-        <v>0.6787</v>
+        <v>0.6836</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.34</v>
+        <v>28.44</v>
       </c>
       <c r="C85" t="n">
-        <v>0.7998</v>
+        <v>0.8036</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8898</v>
+        <v>0.8941</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.15</v>
+        <v>30.18</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8815</v>
+        <v>0.8823</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>26.99</v>
+        <v>27.28</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8749</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.65</v>
+        <v>19.72</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5497</v>
+        <v>0.5562</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.59</v>
+        <v>26.61</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7073</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>36.75</v>
+        <v>37.41</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9698</v>
+        <v>0.9726</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>23.6</v>
+        <v>23.74</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6515</v>
+        <v>0.6632</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>18.41</v>
+        <v>18.53</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6234</v>
+        <v>0.6304999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>28.11</v>
+        <v>28.16</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9173</v>
+        <v>0.9171</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26.86</v>
+        <v>26.94</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7719</v>
+        <v>0.7749</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>19.9</v>
+        <v>19.94</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4218</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24.17</v>
+        <v>24.23</v>
       </c>
       <c r="C97" t="n">
-        <v>0.84</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24.46</v>
+        <v>24.61</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7413</v>
+        <v>0.7499</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.47</v>
+        <v>20.54</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5068</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>24.96</v>
+        <v>25.02</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.7635999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.66</v>
+        <v>25.86</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7265</v>
+        <v>0.7346</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>25.54</v>
+        <v>25.66</v>
       </c>
       <c r="C102" t="n">
-        <v>0.768</v>
+        <v>0.7726</v>
       </c>
     </row>
   </sheetData>
